--- a/Doc/connexions.xlsx
+++ b/Doc/connexions.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c0f9ad4a1d4bd314/DEV/Github/MontureAzimutale/Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{5735B852-9069-489A-A9E8-CF16F7D0DD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B188E018-A3FC-4B99-8270-F3D541DACB5E}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="8_{5735B852-9069-489A-A9E8-CF16F7D0DD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D916EE0F-A84F-4913-A03D-127FFEFA2C6F}"/>
   <bookViews>
-    <workbookView xWindow="-132" yWindow="-132" windowWidth="23304" windowHeight="12504" xr2:uid="{C0124DF5-B963-45A8-8C26-7DEAD7CD6E08}"/>
+    <workbookView xWindow="12" yWindow="216" windowWidth="9372" windowHeight="11196" activeTab="1" xr2:uid="{C0124DF5-B963-45A8-8C26-7DEAD7CD6E08}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Feuil2!$A$25:$J$45</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="125">
   <si>
     <t>GND</t>
   </si>
@@ -174,16 +178,259 @@
   </si>
   <si>
     <t>BI57</t>
+  </si>
+  <si>
+    <t>ESP32</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>DISP</t>
+  </si>
+  <si>
+    <t>RJ45</t>
+  </si>
+  <si>
+    <t>DRV altitude</t>
+  </si>
+  <si>
+    <t>DRV azimutal</t>
+  </si>
+  <si>
+    <t>LM2</t>
+  </si>
+  <si>
+    <t>SW2a</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>txd</t>
+  </si>
+  <si>
+    <t>rxd</t>
+  </si>
+  <si>
+    <t>9-en</t>
+  </si>
+  <si>
+    <t>13-14 slp rst</t>
+  </si>
+  <si>
+    <t>dir</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>2 dc</t>
+  </si>
+  <si>
+    <t>1 cs</t>
+  </si>
+  <si>
+    <t>4 sda</t>
+  </si>
+  <si>
+    <t>5 scl</t>
+  </si>
+  <si>
+    <t>3 rst</t>
+  </si>
+  <si>
+    <t>7 gnd</t>
+  </si>
+  <si>
+    <t>3,3v</t>
+  </si>
+  <si>
+    <t>vcc</t>
+  </si>
+  <si>
+    <t>6 vcc</t>
+  </si>
+  <si>
+    <t>8 vcc</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M0</t>
+  </si>
+  <si>
+    <t>pt diviseur</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
+    <t>G02</t>
+  </si>
+  <si>
+    <t>G03</t>
+  </si>
+  <si>
+    <t>G04</t>
+  </si>
+  <si>
+    <t>G05</t>
+  </si>
+  <si>
+    <t>G06</t>
+  </si>
+  <si>
+    <t>G07</t>
+  </si>
+  <si>
+    <t>G08</t>
+  </si>
+  <si>
+    <t>G09</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>G13</t>
+  </si>
+  <si>
+    <t>G14</t>
+  </si>
+  <si>
+    <t>G15</t>
+  </si>
+  <si>
+    <t>G16</t>
+  </si>
+  <si>
+    <t>G17</t>
+  </si>
+  <si>
+    <t>G18</t>
+  </si>
+  <si>
+    <t>G19</t>
+  </si>
+  <si>
+    <t>G20</t>
+  </si>
+  <si>
+    <t>G21</t>
+  </si>
+  <si>
+    <t>D01</t>
+  </si>
+  <si>
+    <t>D02</t>
+  </si>
+  <si>
+    <t>D03</t>
+  </si>
+  <si>
+    <t>D04</t>
+  </si>
+  <si>
+    <t>D05</t>
+  </si>
+  <si>
+    <t>D06</t>
+  </si>
+  <si>
+    <t>D07</t>
+  </si>
+  <si>
+    <t>D08</t>
+  </si>
+  <si>
+    <t>D09</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>D15</t>
+  </si>
+  <si>
+    <t>D16</t>
+  </si>
+  <si>
+    <t>D17</t>
+  </si>
+  <si>
+    <t>D18</t>
+  </si>
+  <si>
+    <t>D19</t>
+  </si>
+  <si>
+    <t>D20</t>
+  </si>
+  <si>
+    <t>D21</t>
+  </si>
+  <si>
+    <t>G22</t>
+  </si>
+  <si>
+    <t>DRV A A</t>
+  </si>
+  <si>
+    <t>Vmot</t>
+  </si>
+  <si>
+    <t>vers sortie + de SW1</t>
+  </si>
+  <si>
+    <t>vers sortie - de SW1</t>
+  </si>
+  <si>
+    <t>vers CAPA+</t>
+  </si>
+  <si>
+    <t>vers CAPA -</t>
+  </si>
+  <si>
+    <t>connecteur moteur</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -239,7 +486,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -262,11 +509,200 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -313,12 +749,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -341,6 +788,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -661,39 +1112,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF98B75-C9D2-434A-91DE-34B4C7D87258}">
   <dimension ref="A1:BR51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.109375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.109375" style="1" customWidth="1"/>
-    <col min="12" max="13" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.109375" style="1" customWidth="1"/>
     <col min="15" max="15" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="41" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="41" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="5.109375" style="1" customWidth="1"/>
     <col min="45" max="48" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="55" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="62" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="55" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="62" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="11.5546875" style="1"/>
     <col min="69" max="69" width="20.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="70" max="16384" width="11.5546875" style="1"/>
@@ -1552,75 +2003,69 @@
       </c>
     </row>
     <row r="12" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="17"/>
-      <c r="AN12" s="17"/>
-      <c r="AO12" s="17"/>
-      <c r="AP12" s="16"/>
-      <c r="AQ12" s="17"/>
-      <c r="AR12" s="17"/>
-      <c r="AS12" s="17"/>
-      <c r="AT12" s="17"/>
-      <c r="AU12" s="17"/>
-      <c r="AV12" s="17"/>
-      <c r="AW12" s="17"/>
-      <c r="AX12" s="17"/>
-      <c r="AY12" s="17"/>
-      <c r="AZ12" s="17"/>
-      <c r="BA12" s="17"/>
-      <c r="BB12" s="17"/>
-      <c r="BC12" s="17"/>
-      <c r="BD12" s="16"/>
-      <c r="BE12" s="17"/>
-      <c r="BF12" s="17"/>
-      <c r="BG12" s="17"/>
-      <c r="BH12" s="17"/>
-      <c r="BI12" s="17"/>
-      <c r="BJ12" s="17"/>
-      <c r="BK12" s="17"/>
-      <c r="BL12" s="17"/>
-      <c r="BM12" s="17"/>
-      <c r="BN12" s="17"/>
-      <c r="BO12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
+      <c r="AM12" s="16"/>
+      <c r="AN12" s="16"/>
+      <c r="AO12" s="16"/>
+      <c r="AQ12" s="16"/>
+      <c r="AR12" s="16"/>
+      <c r="AS12" s="16"/>
+      <c r="AT12" s="16"/>
+      <c r="AU12" s="16"/>
+      <c r="AV12" s="16"/>
+      <c r="AW12" s="16"/>
+      <c r="AX12" s="16"/>
+      <c r="AY12" s="16"/>
+      <c r="AZ12" s="16"/>
+      <c r="BA12" s="16"/>
+      <c r="BB12" s="16"/>
+      <c r="BC12" s="16"/>
+      <c r="BE12" s="16"/>
+      <c r="BF12" s="16"/>
+      <c r="BG12" s="16"/>
+      <c r="BH12" s="16"/>
+      <c r="BI12" s="16"/>
+      <c r="BJ12" s="16"/>
+      <c r="BK12" s="16"/>
+      <c r="BL12" s="16"/>
+      <c r="BM12" s="16"/>
+      <c r="BN12" s="16"/>
       <c r="BQ12" s="1" t="s">
         <v>19</v>
       </c>
@@ -2950,75 +3395,69 @@
       </c>
     </row>
     <row r="27" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="17"/>
-      <c r="Z27" s="16"/>
-      <c r="AA27" s="17"/>
-      <c r="AB27" s="17"/>
-      <c r="AC27" s="17"/>
-      <c r="AD27" s="17"/>
-      <c r="AE27" s="17"/>
-      <c r="AF27" s="17"/>
-      <c r="AG27" s="17"/>
-      <c r="AH27" s="17"/>
-      <c r="AI27" s="17"/>
-      <c r="AJ27" s="17"/>
-      <c r="AK27" s="17"/>
-      <c r="AL27" s="17"/>
-      <c r="AM27" s="17"/>
-      <c r="AN27" s="17"/>
-      <c r="AO27" s="17"/>
-      <c r="AP27" s="16"/>
-      <c r="AQ27" s="17"/>
-      <c r="AR27" s="17"/>
-      <c r="AS27" s="17"/>
-      <c r="AT27" s="17"/>
-      <c r="AU27" s="17"/>
-      <c r="AV27" s="17"/>
-      <c r="AW27" s="17"/>
-      <c r="AX27" s="17"/>
-      <c r="AY27" s="17"/>
-      <c r="AZ27" s="17"/>
-      <c r="BA27" s="17"/>
-      <c r="BB27" s="17"/>
-      <c r="BC27" s="17"/>
-      <c r="BD27" s="16"/>
-      <c r="BE27" s="17"/>
-      <c r="BF27" s="17"/>
-      <c r="BG27" s="17"/>
-      <c r="BH27" s="17"/>
-      <c r="BI27" s="17"/>
-      <c r="BJ27" s="17"/>
-      <c r="BK27" s="17"/>
-      <c r="BL27" s="17"/>
-      <c r="BM27" s="17"/>
-      <c r="BN27" s="17"/>
-      <c r="BO27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="16"/>
+      <c r="AA27" s="16"/>
+      <c r="AB27" s="16"/>
+      <c r="AC27" s="16"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="16"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="16"/>
+      <c r="AI27" s="16"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
+      <c r="AL27" s="16"/>
+      <c r="AM27" s="16"/>
+      <c r="AN27" s="16"/>
+      <c r="AO27" s="16"/>
+      <c r="AQ27" s="16"/>
+      <c r="AR27" s="16"/>
+      <c r="AS27" s="16"/>
+      <c r="AT27" s="16"/>
+      <c r="AU27" s="16"/>
+      <c r="AV27" s="16"/>
+      <c r="AW27" s="16"/>
+      <c r="AX27" s="16"/>
+      <c r="AY27" s="16"/>
+      <c r="AZ27" s="16"/>
+      <c r="BA27" s="16"/>
+      <c r="BB27" s="16"/>
+      <c r="BC27" s="16"/>
+      <c r="BE27" s="16"/>
+      <c r="BF27" s="16"/>
+      <c r="BG27" s="16"/>
+      <c r="BH27" s="16"/>
+      <c r="BI27" s="16"/>
+      <c r="BJ27" s="16"/>
+      <c r="BK27" s="16"/>
+      <c r="BL27" s="16"/>
+      <c r="BM27" s="16"/>
+      <c r="BN27" s="16"/>
     </row>
     <row r="28" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
@@ -4290,75 +4729,69 @@
       </c>
     </row>
     <row r="42" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="17"/>
-      <c r="Y42" s="17"/>
-      <c r="Z42" s="16"/>
-      <c r="AA42" s="17"/>
-      <c r="AB42" s="17"/>
-      <c r="AC42" s="17"/>
-      <c r="AD42" s="17"/>
-      <c r="AE42" s="17"/>
-      <c r="AF42" s="17"/>
-      <c r="AG42" s="17"/>
-      <c r="AH42" s="17"/>
-      <c r="AI42" s="17"/>
-      <c r="AJ42" s="17"/>
-      <c r="AK42" s="17"/>
-      <c r="AL42" s="17"/>
-      <c r="AM42" s="17"/>
-      <c r="AN42" s="17"/>
-      <c r="AO42" s="17"/>
-      <c r="AP42" s="16"/>
-      <c r="AQ42" s="17"/>
-      <c r="AR42" s="17"/>
-      <c r="AS42" s="17"/>
-      <c r="AT42" s="17"/>
-      <c r="AU42" s="17"/>
-      <c r="AV42" s="17"/>
-      <c r="AW42" s="17"/>
-      <c r="AX42" s="17"/>
-      <c r="AY42" s="17"/>
-      <c r="AZ42" s="17"/>
-      <c r="BA42" s="17"/>
-      <c r="BB42" s="17"/>
-      <c r="BC42" s="17"/>
-      <c r="BD42" s="16"/>
-      <c r="BE42" s="17"/>
-      <c r="BF42" s="17"/>
-      <c r="BG42" s="17"/>
-      <c r="BH42" s="17"/>
-      <c r="BI42" s="17"/>
-      <c r="BJ42" s="17"/>
-      <c r="BK42" s="17"/>
-      <c r="BL42" s="17"/>
-      <c r="BM42" s="17"/>
-      <c r="BN42" s="17"/>
-      <c r="BO42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16"/>
+      <c r="Q42" s="16"/>
+      <c r="R42" s="16"/>
+      <c r="S42" s="16"/>
+      <c r="T42" s="16"/>
+      <c r="U42" s="16"/>
+      <c r="V42" s="16"/>
+      <c r="W42" s="16"/>
+      <c r="X42" s="16"/>
+      <c r="Y42" s="16"/>
+      <c r="AA42" s="16"/>
+      <c r="AB42" s="16"/>
+      <c r="AC42" s="16"/>
+      <c r="AD42" s="16"/>
+      <c r="AE42" s="16"/>
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="16"/>
+      <c r="AI42" s="16"/>
+      <c r="AJ42" s="16"/>
+      <c r="AK42" s="16"/>
+      <c r="AL42" s="16"/>
+      <c r="AM42" s="16"/>
+      <c r="AN42" s="16"/>
+      <c r="AO42" s="16"/>
+      <c r="AQ42" s="16"/>
+      <c r="AR42" s="16"/>
+      <c r="AS42" s="16"/>
+      <c r="AT42" s="16"/>
+      <c r="AU42" s="16"/>
+      <c r="AV42" s="16"/>
+      <c r="AW42" s="16"/>
+      <c r="AX42" s="16"/>
+      <c r="AY42" s="16"/>
+      <c r="AZ42" s="16"/>
+      <c r="BA42" s="16"/>
+      <c r="BB42" s="16"/>
+      <c r="BC42" s="16"/>
+      <c r="BE42" s="16"/>
+      <c r="BF42" s="16"/>
+      <c r="BG42" s="16"/>
+      <c r="BH42" s="16"/>
+      <c r="BI42" s="16"/>
+      <c r="BJ42" s="16"/>
+      <c r="BK42" s="16"/>
+      <c r="BL42" s="16"/>
+      <c r="BM42" s="16"/>
+      <c r="BN42" s="16"/>
     </row>
     <row r="43" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
@@ -5186,4 +5619,652 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC178D78-7308-4943-AD82-CB18627E97A1}">
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="5" width="6.6640625" style="17"/>
+    <col min="6" max="7" width="11" style="17" customWidth="1"/>
+    <col min="8" max="10" width="6.6640625" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19"/>
+      <c r="B1" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="21"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="26"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="17">
+        <v>4</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="26"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="17">
+        <v>5</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="17">
+        <v>6</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="26"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="17">
+        <v>7</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="26"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="17">
+        <v>15</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="17">
+        <v>16</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="26"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="17">
+        <v>17</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" s="26"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="17">
+        <v>18</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="26"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="17">
+        <v>8</v>
+      </c>
+      <c r="E13" s="17">
+        <v>5</v>
+      </c>
+      <c r="J13" s="26"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="17">
+        <v>3</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="26"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="17">
+        <v>46</v>
+      </c>
+      <c r="J15" s="26"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="17">
+        <v>9</v>
+      </c>
+      <c r="E16" s="17">
+        <v>6</v>
+      </c>
+      <c r="J16" s="26"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="17">
+        <v>10</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17" s="26"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="17">
+        <v>11</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="26"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="17">
+        <v>12</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="26"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="17">
+        <v>13</v>
+      </c>
+      <c r="J20" s="26"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="17">
+        <v>14</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J21" s="26"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="26"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="28"/>
+      <c r="J23" s="29"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="23">
+        <v>43</v>
+      </c>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="24"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="17">
+        <v>44</v>
+      </c>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="17">
+        <v>1</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="17">
+        <v>2</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" s="26"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="17">
+        <v>42</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="J29" s="26"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="17">
+        <v>41</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30" s="26"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="17">
+        <v>40</v>
+      </c>
+      <c r="J31" s="26"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="17">
+        <v>39</v>
+      </c>
+      <c r="J32" s="26"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="17">
+        <v>38</v>
+      </c>
+      <c r="J33" s="26"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="17">
+        <v>37</v>
+      </c>
+      <c r="J34" s="26"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="17">
+        <v>36</v>
+      </c>
+      <c r="J35" s="26"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="17">
+        <v>35</v>
+      </c>
+      <c r="J36" s="26"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="17">
+        <v>0</v>
+      </c>
+      <c r="J37" s="26"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="17">
+        <v>45</v>
+      </c>
+      <c r="J38" s="26"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="17">
+        <v>48</v>
+      </c>
+      <c r="J39" s="26"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="17">
+        <v>47</v>
+      </c>
+      <c r="J40" s="26"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="17">
+        <v>21</v>
+      </c>
+      <c r="J41" s="26"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="17">
+        <v>20</v>
+      </c>
+      <c r="J42" s="26"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="17">
+        <v>19</v>
+      </c>
+      <c r="J43" s="26"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="J44" s="26"/>
+    </row>
+    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="I45" s="28"/>
+      <c r="J45" s="29"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B49" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:J45">
+    <sortCondition descending="1" ref="A25:A45"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Doc/connexions.xlsx
+++ b/Doc/connexions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c0f9ad4a1d4bd314/DEV/Github/MontureAzimutale/Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="8_{5735B852-9069-489A-A9E8-CF16F7D0DD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D916EE0F-A84F-4913-A03D-127FFEFA2C6F}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="8_{5735B852-9069-489A-A9E8-CF16F7D0DD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDA778FE-D316-4579-BC7D-20C503567DE7}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="216" windowWidth="9372" windowHeight="11196" activeTab="1" xr2:uid="{C0124DF5-B963-45A8-8C26-7DEAD7CD6E08}"/>
+    <workbookView xWindow="-23148" yWindow="5616" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C0124DF5-B963-45A8-8C26-7DEAD7CD6E08}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="126">
   <si>
     <t>GND</t>
   </si>
@@ -252,9 +252,6 @@
     <t>6 vcc</t>
   </si>
   <si>
-    <t>8 vcc</t>
-  </si>
-  <si>
     <t>M2</t>
   </si>
   <si>
@@ -415,6 +412,12 @@
   </si>
   <si>
     <t>connecteur moteur</t>
+  </si>
+  <si>
+    <t>1/8 vcc</t>
+  </si>
+  <si>
+    <t>2/7 gnd</t>
   </si>
 </sst>
 </file>
@@ -436,7 +439,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,6 +485,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F9B9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -766,6 +775,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5661,7 +5672,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>67</v>
@@ -5677,7 +5688,7 @@
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>67</v>
@@ -5688,14 +5699,14 @@
       <c r="D3" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>70</v>
+      <c r="E3" s="31" t="s">
+        <v>124</v>
       </c>
       <c r="J3" s="26"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>20</v>
@@ -5704,7 +5715,7 @@
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="17">
         <v>4</v>
@@ -5716,7 +5727,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B6" s="17">
         <v>5</v>
@@ -5728,7 +5739,7 @@
     </row>
     <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" s="17">
         <v>6</v>
@@ -5740,7 +5751,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" s="17">
         <v>7</v>
@@ -5752,7 +5763,7 @@
     </row>
     <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B9" s="17">
         <v>15</v>
@@ -5764,7 +5775,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="17">
         <v>16</v>
@@ -5779,7 +5790,7 @@
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="17">
         <v>17</v>
@@ -5791,7 +5802,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="17">
         <v>18</v>
@@ -5803,7 +5814,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="17">
         <v>8</v>
@@ -5815,22 +5826,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B14" s="17">
         <v>3</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>58</v>
-      </c>
       <c r="J14" s="26"/>
     </row>
     <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="17">
         <v>46</v>
@@ -5839,7 +5844,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="17">
         <v>9</v>
@@ -5851,7 +5856,7 @@
     </row>
     <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="17">
         <v>10</v>
@@ -5863,7 +5868,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B18" s="17">
         <v>11</v>
@@ -5875,7 +5880,7 @@
     </row>
     <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="17">
         <v>12</v>
@@ -5887,7 +5892,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="17">
         <v>13</v>
@@ -5896,7 +5901,7 @@
     </row>
     <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" s="17">
         <v>14</v>
@@ -5908,7 +5913,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>16</v>
@@ -5920,7 +5925,7 @@
     </row>
     <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="28" t="s">
         <v>0</v>
@@ -5931,8 +5936,8 @@
       <c r="D23" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="28" t="s">
-        <v>66</v>
+      <c r="E23" s="32" t="s">
+        <v>125</v>
       </c>
       <c r="F23" s="28" t="s">
         <v>54</v>
@@ -5960,7 +5965,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="23">
         <v>43</v>
@@ -5976,7 +5981,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B26" s="17">
         <v>44</v>
@@ -5985,63 +5990,63 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B27" s="17">
         <v>1</v>
       </c>
       <c r="J27" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="17">
         <v>2</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J28" s="26"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="17">
         <v>42</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J29" s="26"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="17">
         <v>41</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J30" s="26"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B31" s="17">
         <v>40</v>
@@ -6050,7 +6055,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32" s="17">
         <v>39</v>
@@ -6059,16 +6064,22 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" s="17">
         <v>38</v>
       </c>
+      <c r="F33" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>58</v>
+      </c>
       <c r="J33" s="26"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B34" s="17">
         <v>37</v>
@@ -6077,7 +6088,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B35" s="17">
         <v>36</v>
@@ -6086,7 +6097,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B36" s="17">
         <v>35</v>
@@ -6095,7 +6106,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" s="17">
         <v>0</v>
@@ -6104,7 +6115,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B38" s="17">
         <v>45</v>
@@ -6113,7 +6124,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B39" s="17">
         <v>48</v>
@@ -6122,7 +6133,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B40" s="17">
         <v>47</v>
@@ -6131,7 +6142,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B41" s="17">
         <v>21</v>
@@ -6140,7 +6151,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B42" s="17">
         <v>20</v>
@@ -6149,7 +6160,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B43" s="17">
         <v>19</v>
@@ -6158,7 +6169,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B44" s="17" t="s">
         <v>0</v>
@@ -6185,7 +6196,7 @@
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B45" s="28" t="s">
         <v>0</v>
@@ -6225,20 +6236,20 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="17" t="s">
         <v>119</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B49" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -6246,17 +6257,17 @@
         <v>0</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B51" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Doc/connexions.xlsx
+++ b/Doc/connexions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c0f9ad4a1d4bd314/DEV/Github/MontureAzimutale/Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="8_{5735B852-9069-489A-A9E8-CF16F7D0DD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDA778FE-D316-4579-BC7D-20C503567DE7}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="8_{5735B852-9069-489A-A9E8-CF16F7D0DD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5744CBF2-BF51-47EA-9F23-56BA7CA1854D}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="5616" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C0124DF5-B963-45A8-8C26-7DEAD7CD6E08}"/>
+    <workbookView xWindow="10995" yWindow="600" windowWidth="14100" windowHeight="14355" activeTab="1" xr2:uid="{C0124DF5-B963-45A8-8C26-7DEAD7CD6E08}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="136">
   <si>
     <t>GND</t>
   </si>
@@ -418,6 +418,36 @@
   </si>
   <si>
     <t>2/7 gnd</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>SLP/RST</t>
+  </si>
+  <si>
+    <t>dc</t>
+  </si>
+  <si>
+    <t>rst</t>
+  </si>
+  <si>
+    <t>mosi</t>
+  </si>
+  <si>
+    <t>sclk</t>
+  </si>
+  <si>
+    <t>sda</t>
+  </si>
+  <si>
+    <t>scl</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>cs</t>
   </si>
 </sst>
 </file>
@@ -439,7 +469,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,6 +521,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -711,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -777,6 +819,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,10 +845,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1123,45 +1165,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF98B75-C9D2-434A-91DE-34B4C7D87258}">
   <dimension ref="A1:BR51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="13.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.109375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.140625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.109375" style="1" customWidth="1"/>
-    <col min="12" max="13" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="41" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="5.109375" style="1" customWidth="1"/>
-    <col min="45" max="48" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="55" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="62" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="11.5546875" style="1"/>
-    <col min="69" max="69" width="20.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="16384" width="11.5546875" style="1"/>
+    <col min="10" max="10" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.140625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="41" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="5.140625" style="1" customWidth="1"/>
+    <col min="45" max="48" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="55" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="62" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="11.5703125" style="1"/>
+    <col min="69" max="69" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="1">
         <v>1</v>
       </c>
@@ -1343,7 +1385,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1424,7 +1466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1505,7 +1547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1580,7 +1622,7 @@
       </c>
       <c r="BR6" s="4"/>
     </row>
-    <row r="7" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -1661,7 +1703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -1762,7 +1804,7 @@
       </c>
       <c r="BR8" s="6"/>
     </row>
-    <row r="9" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -1847,7 +1889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
@@ -1932,7 +1974,7 @@
       </c>
       <c r="BR10" s="7"/>
     </row>
-    <row r="11" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
@@ -2013,7 +2055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -2082,7 +2124,7 @@
       </c>
       <c r="BR12" s="8"/>
     </row>
-    <row r="13" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
@@ -2163,7 +2205,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
@@ -2244,7 +2286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2325,7 +2367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:70" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:70" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
@@ -2406,7 +2448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
@@ -2487,7 +2529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="1">
         <v>1</v>
       </c>
@@ -2669,7 +2711,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>12</v>
       </c>
@@ -2750,7 +2792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>12</v>
       </c>
@@ -2831,7 +2873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>12</v>
       </c>
@@ -2902,7 +2944,7 @@
       <c r="BN21" s="10"/>
       <c r="BO21" s="9"/>
     </row>
-    <row r="22" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>12</v>
       </c>
@@ -3035,7 +3077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>12</v>
       </c>
@@ -3138,7 +3180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>12</v>
       </c>
@@ -3219,7 +3261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>12</v>
       </c>
@@ -3310,7 +3352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>12</v>
       </c>
@@ -3405,7 +3447,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>12</v>
       </c>
@@ -3470,7 +3512,7 @@
       <c r="BM27" s="16"/>
       <c r="BN27" s="16"/>
     </row>
-    <row r="28" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>12</v>
       </c>
@@ -3551,7 +3593,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>12</v>
       </c>
@@ -3632,7 +3674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>12</v>
       </c>
@@ -3713,7 +3755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -3838,7 +3880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>12</v>
       </c>
@@ -3919,7 +3961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>12</v>
       </c>
@@ -3990,7 +4032,7 @@
       <c r="BN33" s="10"/>
       <c r="BO33" s="9"/>
     </row>
-    <row r="34" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>12</v>
       </c>
@@ -4071,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>12</v>
       </c>
@@ -4152,7 +4194,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="1">
         <v>1</v>
       </c>
@@ -4334,7 +4376,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>13</v>
       </c>
@@ -4415,7 +4457,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>13</v>
       </c>
@@ -4496,7 +4538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>13</v>
       </c>
@@ -4577,7 +4619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>13</v>
       </c>
@@ -4658,7 +4700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>13</v>
       </c>
@@ -4739,7 +4781,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
@@ -4804,7 +4846,7 @@
       <c r="BM42" s="16"/>
       <c r="BN42" s="16"/>
     </row>
-    <row r="43" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>13</v>
       </c>
@@ -4885,7 +4927,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>13</v>
       </c>
@@ -4966,7 +5008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>13</v>
       </c>
@@ -5047,7 +5089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>13</v>
       </c>
@@ -5128,7 +5170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>13</v>
       </c>
@@ -5209,7 +5251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>13</v>
       </c>
@@ -5280,7 +5322,7 @@
       <c r="BN48" s="15"/>
       <c r="BO48" s="14"/>
     </row>
-    <row r="49" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>13</v>
       </c>
@@ -5361,7 +5403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>13</v>
       </c>
@@ -5442,7 +5484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:67" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:67" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="1">
         <v>1</v>
       </c>
@@ -5634,15 +5676,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC178D78-7308-4943-AD82-CB18627E97A1}">
-  <dimension ref="A1:J52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="6.6640625" style="17"/>
+    <col min="1" max="5" width="6.7109375" style="17"/>
     <col min="6" max="7" width="11" style="17" customWidth="1"/>
-    <col min="8" max="10" width="6.6640625" style="17"/>
+    <col min="8" max="10" width="6.7109375" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19"/>
       <c r="B1" s="20" t="s">
         <v>46</v>
@@ -5670,7 +5712,7 @@
       </c>
       <c r="J1" s="21"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>116</v>
       </c>
@@ -5686,7 +5728,7 @@
       <c r="I2" s="23"/>
       <c r="J2" s="24"/>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>94</v>
       </c>
@@ -5704,7 +5746,7 @@
       </c>
       <c r="J3" s="26"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>93</v>
       </c>
@@ -5713,7 +5755,7 @@
       </c>
       <c r="J4" s="26"/>
     </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>92</v>
       </c>
@@ -5724,8 +5766,11 @@
         <v>61</v>
       </c>
       <c r="J5" s="26"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L5" s="34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>91</v>
       </c>
@@ -5736,8 +5781,11 @@
         <v>60</v>
       </c>
       <c r="J6" s="26"/>
-    </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L6" s="33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>90</v>
       </c>
@@ -5748,8 +5796,11 @@
         <v>59</v>
       </c>
       <c r="J7" s="26"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L7" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>89</v>
       </c>
@@ -5760,8 +5811,11 @@
         <v>60</v>
       </c>
       <c r="J8" s="26"/>
-    </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L8" s="33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>88</v>
       </c>
@@ -5772,8 +5826,11 @@
         <v>59</v>
       </c>
       <c r="J9" s="26"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L9" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>87</v>
       </c>
@@ -5787,8 +5844,11 @@
         <v>57</v>
       </c>
       <c r="J10" s="26"/>
-    </row>
-    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="33" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>86</v>
       </c>
@@ -5799,8 +5859,11 @@
         <v>56</v>
       </c>
       <c r="J11" s="26"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L11" s="36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>85</v>
       </c>
@@ -5811,8 +5874,11 @@
         <v>55</v>
       </c>
       <c r="J12" s="26"/>
-    </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L12" s="36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>84</v>
       </c>
@@ -5823,8 +5889,11 @@
         <v>5</v>
       </c>
       <c r="J13" s="26"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L13" s="35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>83</v>
       </c>
@@ -5833,7 +5902,7 @@
       </c>
       <c r="J14" s="26"/>
     </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>82</v>
       </c>
@@ -5842,7 +5911,7 @@
       </c>
       <c r="J15" s="26"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +5922,11 @@
         <v>6</v>
       </c>
       <c r="J16" s="26"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L16" s="35" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>80</v>
       </c>
@@ -5865,8 +5937,11 @@
         <v>62</v>
       </c>
       <c r="J17" s="26"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L17" s="34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>79</v>
       </c>
@@ -5877,8 +5952,11 @@
         <v>63</v>
       </c>
       <c r="J18" s="26"/>
-    </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L18" s="34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>78</v>
       </c>
@@ -5889,8 +5967,11 @@
         <v>64</v>
       </c>
       <c r="J19" s="26"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L19" s="34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>77</v>
       </c>
@@ -5898,8 +5979,11 @@
         <v>13</v>
       </c>
       <c r="J20" s="26"/>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L20" s="35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>76</v>
       </c>
@@ -5910,8 +5994,11 @@
         <v>65</v>
       </c>
       <c r="J21" s="26"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L21" s="34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>75</v>
       </c>
@@ -5923,7 +6010,7 @@
       </c>
       <c r="J22" s="26"/>
     </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
         <v>74</v>
       </c>
@@ -5951,7 +6038,7 @@
       <c r="I23" s="28"/>
       <c r="J23" s="29"/>
     </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30"/>
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
@@ -5963,7 +6050,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>115</v>
       </c>
@@ -5979,7 +6066,7 @@
       <c r="I25" s="23"/>
       <c r="J25" s="24"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>114</v>
       </c>
@@ -5988,7 +6075,7 @@
       </c>
       <c r="J26" s="26"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
         <v>113</v>
       </c>
@@ -5998,8 +6085,11 @@
       <c r="J27" s="26" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>112</v>
       </c>
@@ -6013,8 +6103,11 @@
         <v>72</v>
       </c>
       <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L28" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>111</v>
       </c>
@@ -6028,8 +6121,11 @@
         <v>71</v>
       </c>
       <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L29" s="33" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>110</v>
       </c>
@@ -6043,8 +6139,11 @@
         <v>70</v>
       </c>
       <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L30" s="33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
         <v>109</v>
       </c>
@@ -6053,7 +6152,7 @@
       </c>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>108</v>
       </c>
@@ -6061,8 +6160,11 @@
         <v>39</v>
       </c>
       <c r="J32" s="26"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L32" s="33" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
         <v>107</v>
       </c>
@@ -6077,7 +6179,7 @@
       </c>
       <c r="J33" s="26"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
         <v>106</v>
       </c>
@@ -6086,7 +6188,7 @@
       </c>
       <c r="J34" s="26"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
         <v>105</v>
       </c>
@@ -6095,7 +6197,7 @@
       </c>
       <c r="J35" s="26"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
         <v>104</v>
       </c>
@@ -6104,7 +6206,7 @@
       </c>
       <c r="J36" s="26"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
         <v>103</v>
       </c>
@@ -6113,7 +6215,7 @@
       </c>
       <c r="J37" s="26"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
         <v>102</v>
       </c>
@@ -6122,7 +6224,7 @@
       </c>
       <c r="J38" s="26"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
         <v>101</v>
       </c>
@@ -6131,7 +6233,7 @@
       </c>
       <c r="J39" s="26"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>100</v>
       </c>
@@ -6140,7 +6242,7 @@
       </c>
       <c r="J40" s="26"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
         <v>99</v>
       </c>
@@ -6148,8 +6250,11 @@
         <v>21</v>
       </c>
       <c r="J41" s="26"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L41" s="35" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
         <v>98</v>
       </c>
@@ -6158,7 +6263,7 @@
       </c>
       <c r="J42" s="26"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
         <v>97</v>
       </c>
@@ -6167,7 +6272,7 @@
       </c>
       <c r="J43" s="26"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
         <v>96</v>
       </c>
@@ -6194,7 +6299,7 @@
       </c>
       <c r="J44" s="26"/>
     </row>
-    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
         <v>95</v>
       </c>
@@ -6222,7 +6327,7 @@
       <c r="I45" s="28"/>
       <c r="J45" s="29"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="18"/>
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
@@ -6234,12 +6339,12 @@
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
         <v>118</v>
       </c>
@@ -6247,12 +6352,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" s="17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
         <v>0</v>
       </c>
@@ -6260,12 +6365,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" s="17" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
         <v>123</v>
       </c>
